--- a/Documentation/BOM.xlsx
+++ b/Documentation/BOM.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4460,74 +4460,70 @@
       <c r="I116" s="13" t="inlineStr"/>
     </row>
     <row r="117" ht="30" customHeight="1">
-      <c r="A117" s="14" t="inlineStr">
-        <is>
-          <t>Transformer</t>
-        </is>
-      </c>
-      <c r="B117" s="14" t="inlineStr">
-        <is>
-          <t>LP / LS</t>
-        </is>
-      </c>
-      <c r="C117" s="14" t="inlineStr">
-        <is>
-          <t>14µH / 2.33µH</t>
-        </is>
-      </c>
-      <c r="D117" s="14" t="inlineStr">
-        <is>
-          <t>FT-114-61 ferrite (AL=75); 15T primary : 6T secondary; 300Ω balanced → 50Ω unbal; 6.25:1 Z ratio; good through 10m</t>
-        </is>
-      </c>
-      <c r="E117" s="15" t="inlineStr">
-        <is>
-          <t>Balun</t>
-        </is>
-      </c>
-      <c r="F117" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="14" t="inlineStr"/>
-      <c r="H117" s="14" t="inlineStr">
-        <is>
-          <t>Amidon / Kits&amp;Parts</t>
-        </is>
-      </c>
-      <c r="I117" s="15" t="inlineStr"/>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>U_HBEAT</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>74HC4538</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Dual retriggerable monostable (DIP-16). One section used. R_RC + C_RC sets the retrigger window — pick R = 100 kΩ, C = 2.2 µF for ~220 ms hold. Output Q drives Q_HBEAT base. Pin 1 (A trigger) = MCU GPIO; pin 4 (Q) = relay drive</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Mains Interlock</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="3" t="inlineStr"/>
     </row>
     <row r="118" ht="30" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>Capacitor</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>C1, C3</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>300pF</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>NP0/C0G 1–2%; 5-pole 0.5dB Chebyshev LPF fc=18MHz; end caps</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>LPF (50Ω)</t>
-        </is>
-      </c>
-      <c r="F118" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="6" t="inlineStr"/>
-      <c r="I118" s="7" t="inlineStr"/>
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>R_HBEAT_T</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>100kΩ</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Metal film 1%; 4538 timing resistor (pin 14 to VCC). With C_HBEAT_T = 2.2 µF gives ~220 ms hold</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>Mains Interlock</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr"/>
+      <c r="I118" s="5" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
@@ -4537,22 +4533,22 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C_HBEAT_T</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>450pF</t>
+          <t>2.2µF</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>NP0/C0G 1–2%; 5-pole Chebyshev LPF centre cap</t>
+          <t>Film MKT 50 V; 4538 timing capacitor (pin 15 to GND). Tantalum / electrolytic OK if leakage low</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>LPF (50Ω)</t>
+          <t>Mains Interlock</t>
         </is>
       </c>
       <c r="F119" s="7" t="n">
@@ -4563,46 +4559,347 @@
       <c r="I119" s="7" t="inlineStr"/>
     </row>
     <row r="120" ht="30" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>R_HBEAT_PD</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>10kΩ</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Metal film 1/4 W; external pull-down on MAINS_HEARTBEAT GPIO trace. Guarantees relay OFF when MCU is unpowered, in reset, or removed</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Mains Interlock</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="4" t="inlineStr"/>
+      <c r="H120" s="4" t="inlineStr"/>
+      <c r="I120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121" ht="30" customHeight="1">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>Semiconductor</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>Q_HBEAT</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>2N3904</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>NPN small-signal switch (TO-92); 4538 Q output → K_MAIN coil low-side. Alt: BSS138 SOT-23 if going SMT</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>Mains Interlock</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="10" t="inlineStr"/>
+      <c r="H121" s="10" t="inlineStr"/>
+      <c r="I121" s="11" t="inlineStr"/>
+    </row>
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>R_HBEAT_B</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>4.7kΩ</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Metal film 1/4 W; Q_HBEAT base-current limiter from the 4538 output</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Mains Interlock</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="4" t="inlineStr"/>
+      <c r="H122" s="4" t="inlineStr"/>
+      <c r="I122" s="5" t="inlineStr"/>
+    </row>
+    <row r="123" ht="30" customHeight="1">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>Semiconductor</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>D_HBEAT_FW</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>1N4148</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>Flyback diode across K_MAIN coil — catches the kickback when Q_HBEAT switches off. Alt: 1N4001 for higher coil current relays</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>Mains Interlock</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="10" t="inlineStr"/>
+      <c r="H123" s="10" t="inlineStr"/>
+      <c r="I123" s="11" t="inlineStr"/>
+    </row>
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>K_MAIN</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Omron G7L-2A-T (or similar)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>AC mains power relay, SPST-NO (or DPST-NO for double-pole switching of L+N), 12 V DC coil, contacts rated 250 V AC / 10 A min — sized for the rig's peak transformer inrush (factor ~10× steady-state). DIN-rail mount alternatives: Schrack RT, Omron MY series. Avoid sub-1 A "signal" relays — AC inrush will pit them</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>Mains Interlock</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125" ht="30" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>C_K_BYP</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>100nF X7R</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>K_MAIN coil supply bypass (12 V → GND), close to the relay coil</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>Mains Interlock</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="6" t="inlineStr"/>
+      <c r="H125" s="6" t="inlineStr"/>
+      <c r="I125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="14" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="inlineStr">
+        <is>
+          <t>LP / LS</t>
+        </is>
+      </c>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>14µH / 2.33µH</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="inlineStr">
+        <is>
+          <t>FT-114-61 ferrite (AL=75); 15T primary : 6T secondary; 300Ω balanced → 50Ω unbal; 6.25:1 Z ratio; good through 10m</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="inlineStr">
+        <is>
+          <t>Balun</t>
+        </is>
+      </c>
+      <c r="F126" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="14" t="inlineStr"/>
+      <c r="H126" s="14" t="inlineStr">
+        <is>
+          <t>Amidon / Kits&amp;Parts</t>
+        </is>
+      </c>
+      <c r="I126" s="15" t="inlineStr"/>
+    </row>
+    <row r="127" ht="30" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>C1, C3</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>300pF</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>NP0/C0G 1–2%; 5-pole 0.5dB Chebyshev LPF fc=18MHz; end caps</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>LPF (50Ω)</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G127" s="6" t="inlineStr"/>
+      <c r="H127" s="6" t="inlineStr"/>
+      <c r="I127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>450pF</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>NP0/C0G 1–2%; 5-pole Chebyshev LPF centre cap</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>LPF (50Ω)</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr"/>
+      <c r="I128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129" ht="30" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t>Inductor</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>L1, L2</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr">
+      <c r="C129" s="8" t="inlineStr">
         <is>
           <t>540nH</t>
         </is>
       </c>
-      <c r="D120" s="8" t="inlineStr">
+      <c r="D129" s="8" t="inlineStr">
         <is>
           <t>T-68-6 (Mix 6, yellow); ~11T #26AWG; 5-pole Chebyshev LPF series arms</t>
         </is>
       </c>
-      <c r="E120" s="9" t="inlineStr">
+      <c r="E129" s="9" t="inlineStr">
         <is>
           <t>LPF (50Ω)</t>
         </is>
       </c>
-      <c r="F120" s="9" t="n">
+      <c r="F129" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G120" s="8" t="inlineStr"/>
-      <c r="H120" s="8" t="inlineStr">
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="8" t="inlineStr">
         <is>
           <t>Amidon / Kits&amp;Parts</t>
         </is>
       </c>
-      <c r="I120" s="9" t="inlineStr"/>
+      <c r="I129" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,Ordered,No"</formula1>
     </dataValidation>
   </dataValidations>
